--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260806.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.32%</t>
+          <t>11.42%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.67%</t>
+          <t>10.55%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.13%</t>
+          <t>8.10%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.86%</t>
+          <t>7.73%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.19%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>22,431</t>
+          <t>24,204</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,22 +909,22 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>24,204</t>
+          <t>22,431</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>30,345</t>
+          <t>94,763</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>94,763</t>
+          <t>30,345</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1166,95 +1166,95 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>11,337</t>
+          <t>27,469</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>27,469</t>
+          <t>11,337</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>30,214</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>30,214</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1371,44 +1371,44 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>10,646</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10,646</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1474,24 +1474,24 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,22 +1503,22 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,839</t>
+          <t>8,021</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,021</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>120,376,677</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
